--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487131_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487131_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.597300000000001</v>
+        <v>8.9747</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3421</v>
+        <v>6.4423</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2552</v>
+        <v>2.5324</v>
       </c>
       <c r="G2" t="n">
         <v>6.73</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.0866</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3437</v>
+        <v>-0.2435</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0529</v>
+        <v>0.3301</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1837</v>
+        <v>5.1747</v>
       </c>
       <c r="E3" t="n">
-        <v>4.31</v>
+        <v>3.4109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8736</v>
+        <v>1.7639</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4228</v>
+        <v>3.5492</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3375</v>
+        <v>3.2757</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0853</v>
+        <v>0.2735</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9512</v>
+        <v>3.0752</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5731</v>
+        <v>3.5964</v>
       </c>
       <c r="L3" t="n">
-        <v>3.378</v>
+        <v>-0.5212</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5283</v>
+        <v>0.474</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2356</v>
+        <v>-0.3207</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2928</v>
+        <v>0.7947</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4098</v>
+        <v>-0.3745</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3239</v>
+        <v>-0.2131</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0859</v>
+        <v>-0.1613</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5669</v>
+        <v>5.03</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9101</v>
+        <v>4.2099</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6568</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5492</v>
+        <v>3.4228</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2757</v>
+        <v>0.3375</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2735</v>
+        <v>3.0853</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0752</v>
+        <v>4.9512</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5964</v>
+        <v>1.5731</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5212</v>
+        <v>3.378</v>
       </c>
       <c r="M4" t="n">
-        <v>0.474</v>
+        <v>-1.5283</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3207</v>
+        <v>-1.2356</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7947</v>
+        <v>-0.2928</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9822</v>
+        <v>0.2561</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7139</v>
+        <v>0.2238</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2684</v>
+        <v>0.0324</v>
       </c>
       <c r="V4" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3828</v>
+        <v>3.3224</v>
       </c>
       <c r="E5" t="n">
-        <v>2.093</v>
+        <v>1.9522</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2899</v>
+        <v>1.3702</v>
       </c>
       <c r="G5" t="n">
         <v>4.9433</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5255</v>
+        <v>-0.586</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1057</v>
+        <v>-0.2465</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4197</v>
+        <v>-0.3394</v>
       </c>
       <c r="V5" t="n">
         <v>-1.228</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4654</v>
+        <v>2.8858</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0023</v>
+        <v>1.2621</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4631</v>
+        <v>1.6237</v>
       </c>
       <c r="G6" t="n">
         <v>1.8024</v>
@@ -922,13 +922,13 @@
         <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2744</v>
+        <v>-0.854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6398</v>
+        <v>-0.38</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.4739</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5717</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8638</v>
+        <v>1.8836</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7562</v>
+        <v>1.8563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1076</v>
+        <v>0.0273</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8692</v>
@@ -1000,13 +1000,13 @@
         <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.154</v>
+        <v>0.1738</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1468</v>
+        <v>0.2469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0073</v>
+        <v>-0.0731</v>
       </c>
       <c r="V7" t="n">
         <v>1.228</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.4452</v>
       </c>
       <c r="E8" t="n">
-        <v>0.788</v>
+        <v>0.3875</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2099</v>
+        <v>0.0578</v>
       </c>
       <c r="G8" t="n">
         <v>0.1416</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2234</v>
+        <v>-0.3563</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4429</v>
+        <v>0.0423</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6663</v>
+        <v>-0.3986</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2702</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2946</v>
+        <v>-0.099</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3588</v>
+        <v>-1.0648</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6535</v>
+        <v>0.9658</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5389</v>
+        <v>-1.1297</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1137</v>
+        <v>-1.6973</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5748</v>
+        <v>0.5677</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2531</v>
+        <v>0.7124</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2938</v>
+        <v>-0.5486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>1.261</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7141999999999999</v>
+        <v>-1.842</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1801</v>
+        <v>-1.1487</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5341</v>
+        <v>-0.6933</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>3.0881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8335</v>
+        <v>-0.3903</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8593</v>
+        <v>-0.11</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0258</v>
+        <v>-0.2803</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>D. PÉREZ DE SAN ROMÁN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2586</v>
+        <v>-0.3478</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2245</v>
+        <v>-0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9658</v>
+        <v>-0.2289</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1297</v>
+        <v>-0.2735</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6973</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5677</v>
+        <v>-0.2735</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7124</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5486</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.261</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.842</v>
+        <v>-0.2735</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1487</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6933</v>
+        <v>-0.2735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0881</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2697</v>
+        <v>-0.119</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2803</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. PÉREZ DE SAN ROMÁN</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3746</v>
+        <v>-0.4202</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.119</v>
+        <v>-2.1005</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2556</v>
+        <v>1.6803</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2735</v>
+        <v>-0.5389</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.1137</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2735</v>
+        <v>0.5748</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.2531</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-1.2938</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2735</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.1801</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2735</v>
+        <v>0.5341</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1011</v>
+        <v>0.1186</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>0.1177</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0178</v>
+        <v>0.001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2508</v>
+        <v>-1.5627</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2688</v>
+        <v>0.2319</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.982</v>
+        <v>-1.7946</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5951</v>
@@ -1390,13 +1390,13 @@
         <v>2.3161</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.049</v>
+        <v>-0.3609</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6398</v>
+        <v>-0.1391</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4092</v>
+        <v>-0.2218</v>
       </c>
       <c r="V12" t="n">
         <v>0.0422</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.323</v>
+        <v>-3.2635</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6392</v>
+        <v>-2.5798</v>
       </c>
       <c r="F13" t="n">
         <v>-0.6838</v>
@@ -1468,10 +1468,10 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2234</v>
+        <v>-0.1639</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1468</v>
+        <v>0.2062</v>
       </c>
       <c r="U13" t="n">
         <v>-0.3702</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.7256</v>
+        <v>22.0232</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5914</v>
+        <v>13.889</v>
       </c>
       <c r="F14" t="n">
         <v>8.134200000000002</v>
@@ -1513,7 +1513,7 @@
         <v>12.5742</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.0407</v>
+        <v>-5.040699999999999</v>
       </c>
       <c r="I14" t="n">
         <v>17.615</v>
@@ -1522,7 +1522,7 @@
         <v>19.4146</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3065</v>
+        <v>2.306500000000001</v>
       </c>
       <c r="L14" t="n">
         <v>17.108</v>
@@ -1534,7 +1534,7 @@
         <v>-7.3472</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5067999999999997</v>
+        <v>0.5067999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>12.5457</v>
@@ -1546,13 +1546,13 @@
         <v>24.126</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8224</v>
+        <v>-2.5252</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9118999999999999</v>
+        <v>-0.6143000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9106</v>
+        <v>-1.9105</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5717000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4686</v>
+        <v>1.168</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3161</v>
+        <v>1.4176</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7846</v>
+        <v>-0.2496</v>
       </c>
       <c r="G15" t="n">
         <v>0.9903999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7219</v>
+        <v>-0.0853</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1752</v>
+        <v>-0.0737</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5467</v>
+        <v>-0.0116</v>
       </c>
       <c r="V15" t="n">
         <v>1.228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5077</v>
+        <v>-0.2201</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0432</v>
+        <v>0.1433</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.3635</v>
       </c>
       <c r="G16" t="n">
         <v>0.3179</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4396</v>
+        <v>-0.152</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7484</v>
       </c>
       <c r="E17" t="n">
         <v>0.0231</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7443</v>
+        <v>-0.7714</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5621</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6359</v>
+        <v>0.6088</v>
       </c>
       <c r="T17" t="n">
         <v>0.1917</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4442</v>
+        <v>0.4171</v>
       </c>
       <c r="V17" t="n">
         <v>2.1701</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8521</v>
+        <v>-1.0723</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1378</v>
+        <v>-0.4382</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7144</v>
+        <v>-0.6341</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4543</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4092</v>
+        <v>0.189</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4891</v>
+        <v>0.1887</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5096</v>
+        <v>-1.4514</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0369</v>
+        <v>0.8677</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4727</v>
+        <v>-2.3191</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3464</v>
+        <v>-0.5335</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9801</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3663</v>
+        <v>-0.4591</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5855</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6262</v>
+        <v>0.1863</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0.6348</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7609</v>
+        <v>-1.3546</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3539</v>
+        <v>-0.2607</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.407</v>
+        <v>-1.0939</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4508</v>
+        <v>-0.234</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5486</v>
+        <v>0.0466</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0978</v>
+        <v>-0.2806</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>-1.842</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6186</v>
+        <v>-1.6564</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9678</v>
+        <v>-0.2372</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5864</v>
+        <v>-1.4192</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5335</v>
+        <v>-1.3464</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.9801</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4591</v>
+        <v>-0.3663</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8211000000000001</v>
+        <v>-0.5855</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1863</v>
+        <v>-0.6262</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6348</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3546</v>
+        <v>-0.7609</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2607</v>
+        <v>-0.3539</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0939</v>
+        <v>-0.407</v>
       </c>
       <c r="P20" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4012</v>
+        <v>0.3041</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1468</v>
+        <v>0.3483</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.548</v>
+        <v>-0.0443</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.842</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.842</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0033</v>
+        <v>-2.5428</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1777</v>
+        <v>-1.4062</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8257</v>
+        <v>-1.1366</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4242</v>
+        <v>-1.7016</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1914</v>
+        <v>-0.4399</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.7672</v>
+        <v>-1.2617</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8867</v>
+        <v>1.0676</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5058</v>
+        <v>0.4085</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.619</v>
+        <v>0.6591</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4625</v>
+        <v>-2.7692</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3144</v>
+        <v>-0.8484</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.1481</v>
+        <v>-1.9207</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6672</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.7902</v>
+        <v>-3.8602</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7378</v>
+        <v>0.4749</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7681</v>
+        <v>0.4865</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9697</v>
+        <v>-0.0116</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4982</v>
+        <v>0.614</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0422</v>
+        <v>0.8999</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1419</v>
+        <v>-2.8059</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0056</v>
+        <v>-1.9328</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1362</v>
+        <v>-0.8731</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7016</v>
+        <v>-2.6724</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4399</v>
+        <v>0.3965</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2617</v>
+        <v>-3.0689</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0676</v>
+        <v>-1.2117</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4085</v>
+        <v>0.0828</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6591</v>
+        <v>-1.2945</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7692</v>
+        <v>-1.4607</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8484</v>
+        <v>0.3137</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9207</v>
+        <v>-1.7743</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9301</v>
+        <v>-0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8758</v>
+        <v>0.8242</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8871</v>
+        <v>0.2439</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0113</v>
+        <v>0.5803</v>
       </c>
       <c r="V22" t="n">
-        <v>0.614</v>
+        <v>-0.5717</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2859</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2997</v>
+        <v>-3.6485</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5337</v>
+        <v>-0.7785</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.766</v>
+        <v>-2.87</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6724</v>
+        <v>1.4242</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3965</v>
+        <v>5.1914</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0689</v>
+        <v>-3.7672</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2117</v>
+        <v>4.8867</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0828</v>
+        <v>5.5058</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2945</v>
+        <v>-0.619</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4607</v>
+        <v>-3.4625</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3137</v>
+        <v>-0.3144</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7743</v>
+        <v>-3.1481</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.386</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-5.7902</v>
       </c>
       <c r="R23" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3305</v>
+        <v>1.0926</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3569</v>
+        <v>0.1673</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6874</v>
+        <v>0.9253</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5717</v>
+        <v>-2.4982</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5717</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2028</v>
+        <v>-3.8816</v>
       </c>
       <c r="E24" t="n">
         <v>-3.3144</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8885</v>
+        <v>-0.5672</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4075</v>
@@ -2326,13 +2326,13 @@
         <v>0.772</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0648</v>
+        <v>0.386</v>
       </c>
       <c r="T24" t="n">
         <v>0.2512</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1864</v>
+        <v>0.1348</v>
       </c>
       <c r="V24" t="n">
         <v>1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4001</v>
+        <v>-4.1989</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2784</v>
+        <v>-2.4787</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1217</v>
+        <v>-1.7202</v>
       </c>
       <c r="G25" t="n">
         <v>-2.629</v>
@@ -2404,13 +2404,13 @@
         <v>1.3511</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1196</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5169</v>
+        <v>0.3166</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.235</v>
       </c>
       <c r="V25" t="n">
         <v>0.8576</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.7257</v>
+        <v>-21.0583</v>
       </c>
       <c r="E26" t="n">
         <v>-8.1343</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.5914</v>
+        <v>-12.924</v>
       </c>
       <c r="G26" t="n">
         <v>-12.5743</v>
@@ -2455,10 +2455,10 @@
         <v>-17.615</v>
       </c>
       <c r="J26" t="n">
-        <v>6.840199999999999</v>
+        <v>6.840200000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>7.3471</v>
+        <v>7.347099999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-0.5066000000000002</v>
@@ -2482,19 +2482,19 @@
         <v>11.5804</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8225</v>
+        <v>3.4899</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9105</v>
+        <v>1.9103</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9118999999999997</v>
+        <v>1.5795</v>
       </c>
       <c r="V26" t="n">
         <v>0.5718000000000002</v>
       </c>
       <c r="W26" t="n">
-        <v>7.241200000000001</v>
+        <v>7.241199999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-6.6694</v>
